--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/ALABAMA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/ALABAMA_2015.xlsx
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C101">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C139">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C237">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C624">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C625">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C654">
